--- a/deliverables/exports/track-b/10-lead-magnet-scorecard.xlsx
+++ b/deliverables/exports/track-b/10-lead-magnet-scorecard.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -557,152 +557,159 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Each is a thing a North American buyer verifies. None is a skill.</t>
+          <t>&gt; **Unresolved, see `00-CONFLICTS-TO-RESOLVE.md` conflict 1.** These six were &gt; reasoned, not evidenced. The Block 1 research supplies the buyer's actual &gt; verification sequence and it does not match. Four of the six survive. Pricing &gt; frame does not appear anywhere in the buyer's checks. Security evidence, tax &gt; documentation and insurance are all missing here and are three of the four most &gt; common foreign-vendor gaps. Left as written pending your decision, because &gt; changing them changes the whole top of funnel.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>Each is a thing a North American buyer verifies. None is a skill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Questions</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Seven questions. Each maps to one dimension, with question 7 covering dimension 6 and capturing the segmentation signal. Answer options are ordered low to high and score 0, 4, 8, 12, 16.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>**Question 7 does the commercial work.** Phase 4 concluded that the paid room is built for members with a live deal, and this question finds them. Respondents answering (c), (d) or (e) go to a founding cohort conversation regardless of total score. Respondents answering (a) go to the email sequence and stay there until something changes.</t>
+          <t>Seven questions. Each maps to one dimension, with question 7 covering dimension 6 and capturing the segmentation signal. Answer options are ordered low to high and score 0, 4, 8, 12, 16.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>**Question 7 does the commercial work.** Phase 4 concluded that the paid room is built for members with a live deal, and this question finds them. Respondents answering (c), (d) or (e) go to a founding cohort conversation regardless of total score. Respondents answering (a) go to the email sequence and stay there until something changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Results tiers</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Total range 0 to 112. Bands set on that range.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>**Wording discipline.** Read the low tier message again. It opens by conceding capability. That opening is not politeness, it is the positioning: the premise of this entire business is that the capability is already there. A scorecard that opens by implying otherwise contradicts the offer it is selling and insults the audience while doing it.</t>
+          <t>Total range 0 to 112. Bands set on that range.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>**Never:** a "risk" framing, a grade, a percentile against other respondents, or any number about money. Scores are per dimension, never a single verdict.</t>
+          <t>**Wording discipline.** Read the low tier message again. It opens by conceding capability. That opening is not politeness, it is the positioning: the premise of this entire business is that the capability is already there. A scorecard that opens by implying otherwise contradicts the offer it is selling and insults the audience while doing it.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>**Never:** a "risk" framing, a grade, a percentile against other respondents, or any number about money. Scores are per dimension, never a single verdict.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Post-scorecard email sequence</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Four emails, Arabic. **Segmented by weakest dimension**, not sent flat. A single sequence to everyone throws away the qualification the scorecard just performed.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>Four emails, Arabic. **Segmented by weakest dimension**, not sent flat. A single sequence to everyone throws away the qualification the scorecard just performed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
           <t>**Email 4 disqualifies on purpose.** It carries the exclusions from Phase 8 and the terms from Phase 6 RTB 3.3. In a category with a justified trust problem, and against a buyer whose internal decision maker is asking whether this is another course, an email that tells people not to buy is the one that converts the people who should.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Segmentation map</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>The contracting row matters twice. A respondent whose weakest dimension is payment and contracting is telling you they cannot easily receive money across a border, which strongly predicts they will also struggle to send it. Flag them before they reach a checkout that will decline, and route them to the annual or local option directly.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>The contracting row matters twice. A respondent whose weakest dimension is payment and contracting is telling you they cannot easily receive money across a border, which strongly predicts they will also struggle to send it. Flag them before they reach a checkout that will decline, and route them to the annual or local option directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Implementation notes for ScoreApp</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Why this converts</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>It hands over the buyer's checklist for free and in full, which is the thing the audience most wants and cannot get anywhere in the verified competitor set. Then it shows the respondent their own position against it, in their own words, before anything is sold.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>It hands over the buyer's checklist for free and in full, which is the thing the audience most wants and cannot get anywhere in the verified competitor set. Then it shows the respondent their own position against it, in their own words, before anything is sold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>What it cannot hand over is the application of that checklist to the respondent's own live deal, because that requires a person looking at a specific document. That is the paid offer, and the scorecard makes the boundary between the two obvious without having to argue for it.</t>
         </is>

--- a/deliverables/exports/track-b/10-lead-magnet-scorecard.xlsx
+++ b/deliverables/exports/track-b/10-lead-magnet-scorecard.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -557,161 +557,182 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>&gt; **Unresolved, see `00-CONFLICTS-TO-RESOLVE.md` conflict 1.** These six were &gt; reasoned, not evidenced. The Block 1 research supplies the buyer's actual &gt; verification sequence and it does not match. Four of the six survive. Pricing &gt; frame does not appear anywhere in the buyer's checks. Security evidence, tax &gt; documentation and insurance are all missing here and are three of the four most &gt; common foreign-vendor gaps. Left as written pending your decision, because &gt; changing them changes the whole top of funnel.</t>
+          <t>**Rebuilt on evidence.** Conflicts 1 and 7 resolved in `00-RESOLUTIONS.md`. The previous six were reasoned. These come from `00-BUYER-CHECKS.md`, and each one's answer options are the rungs of that dimension's ladder, so the result is a band position rather than an impression.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Each is a thing a North American buyer verifies. None is a skill.</t>
+          <t>The fourth column is the split promise from conflict 3, built into the instrument itself. A respondent sees not only where they are weak but which weaknesses cost money to close.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>**What changed and why.** Pricing frame was removed. It is a real problem and it is not something a buyer verifies, so it has no place in an instrument that claims to report what buyers check. It moves into the teaching. Security and compliance readiness replaces it, because it is the dominant gate above band 2 and the previous version had no dimension for it at all. Follow-through became Champion enablement, which is the mechanism the research actually describes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Questions</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Seven questions. Each maps to one dimension, with question 7 covering dimension 6 and capturing the segmentation signal. Answer options are ordered low to high and score 0, 4, 8, 12, 16.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>**Question 7 does the commercial work.** Phase 4 concluded that the paid room is built for members with a live deal, and this question finds them. Respondents answering (c), (d) or (e) go to a founding cohort conversation regardless of total score. Respondents answering (a) go to the email sequence and stay there until something changes.</t>
+          <t>Seven questions. Six dimensions plus the segmentation signal. Options are ordered low to high and score 0, 4, 8, 12, 16.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Question 6 is the one to watch.** It is the newest, it comes directly from the research finding that deals stall because the champion cannot sell internally, and almost every respondent will answer (a) or (b). It is free to fix, it needs no purchase, and demonstrating it in the result email is the strongest possible argument that this instrument knows something the respondent does not.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>**Question 7 still does the commercial work.** Respondents answering (c), (d) or (e) go to a founding cohort conversation regardless of total score. Respondents answering (a) go to the email sequence and stay there until something changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Results tiers</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Total range 0 to 112. Bands set on that range.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>**Wording discipline.** Read the low tier message again. It opens by conceding capability. That opening is not politeness, it is the positioning: the premise of this entire business is that the capability is already there. A scorecard that opens by implying otherwise contradicts the offer it is selling and insults the audience while doing it.</t>
+          <t>Total range 0 to 112. Bands map to the deal bands in `00-RESOLUTIONS.md`, so the result tells a respondent what size of deal their current setup can survive.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>**Never:** a "risk" framing, a grade, a percentile against other respondents, or any number about money. Scores are per dimension, never a single verdict.</t>
+          <t>**Wording discipline, and it survives the rebuild.** The low band message still opens by conceding capability, because that is the premise of the business. It now also does something the old version did not: it says band 1 is a real place to be rather than a deficiency. An audience earning a living on marketplaces is not failing, and telling them they are loses them in the first sentence.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**The stated absence, conflict 5.** The result page carries a plain line that Arab Tech Export has no published results yet, and what stands in its place. An audience sceptical of this category reads an unexplained absence as concealment.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>**Never:** a risk framing, a grade, a percentile against other respondents, or any number about money. Scores are per dimension plus a band, never a single verdict. The band describes what process a setup can survive. It never implies an income.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Post-scorecard email sequence</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Four emails, Arabic. **Segmented by weakest dimension**, not sent flat. A single sequence to everyone throws away the qualification the scorecard just performed.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>Four emails, Arabic. **Segmented by weakest dimension**, not sent flat. A single sequence to everyone throws away the qualification the scorecard just performed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t>**Email 4 disqualifies on purpose.** It carries the exclusions from Phase 8 and the terms from Phase 6 RTB 3.3. In a category with a justified trust problem, and against a buyer whose internal decision maker is asking whether this is another course, an email that tells people not to buy is the one that converts the people who should.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Segmentation map</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>The contracting row matters twice. A respondent whose weakest dimension is payment and contracting is telling you they cannot easily receive money across a border, which strongly predicts they will also struggle to send it. Flag them before they reach a checkout that will decline, and route them to the annual or local option directly.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
+          <t>**The paperwork variant is the sequence's best asset.** It carries a primary-sourced, checkable, financially specific fact that almost no respondent knows, it costs nothing to act on, and it is verifiable against the IRS rather than against us. For a pre-launch business with no proof of its own, an email that is right about something expensive is the closest thing to a credential available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>**Security readiness routes carefully.** A respondent weak here at band 1 does not have a problem yet. The variant should say so rather than manufacture urgency, then show what the ladder looks like. Selling SOC 2 anxiety to someone bidding $4,000 projects is the churn event Phase 7 warns about, dressed as a conversion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Implementation notes for ScoreApp</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Implementation notes for ScoreApp</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Why this converts</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>It hands over the buyer's checklist for free and in full, which is the thing the audience most wants and cannot get anywhere in the verified competitor set. Then it shows the respondent their own position against it, in their own words, before anything is sold.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>What it cannot hand over is the application of that checklist to the respondent's own live deal, because that requires a person looking at a specific document. That is the paid offer, and the scorecard makes the boundary between the two obvious without having to argue for it.</t>
+          <t>It hands over the buyer's checklist for free and in full, which is the thing the audience most wants and cannot get anywhere in the verified competitor set. The checklist is now evidenced rather than asserted, which is what the Block 1 research bought. Then it shows the respondent their own position against it, in their own words, before anything is sold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>What it cannot hand over is the application of that checklist to the respondent's own live deal, because that requires a person looking at a specific document. That is the paid offer, and the scorecard makes the boundary obvious without having to argue it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>**What the rebuild added.** The band result gives the respondent somewhere to go. The old version told them what they were missing. This one tells them what size of deal their setup currently survives and what the next rung costs, which is a reason to stay in touch even when they are not ready to buy. That is the ladder working as positioning, per `00-RESOLUTIONS.md` conflict 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>**What it must never imply.** That clearing these checks wins the deal. It makes a vendor eligible. Phase 3 flags this as the claim most likely to be crossed later, and a scorecard that returns a band is exactly where someone would cross it.</t>
         </is>
       </c>
     </row>
@@ -823,12 +844,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -854,6 +876,11 @@
           <t>What the buyer is checking</t>
         </is>
       </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Free to fix, or has to be built</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
@@ -869,6 +896,11 @@
           <t>Can they tell what you do in one line, in their category language</t>
         </is>
       </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -881,7 +913,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Is there anything they can verify without asking you</t>
+          <t>Is there anything attributable they can verify without asking you</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Free to start, costs time to accumulate</t>
         </is>
       </c>
     </row>
@@ -899,6 +936,11 @@
           <t>Is the work defined so they know what they are buying and when it ends</t>
         </is>
       </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -906,12 +948,17 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Pricing frame</t>
+          <t>Paperwork readiness</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Is the price attached to a problem, or to your hours</t>
+          <t>Tax form, contract template, invoicing that matches their records, insurance</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Mixed. The tax form is free. Insurance is not</t>
         </is>
       </c>
     </row>
@@ -921,12 +968,17 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Contracting and payment</t>
+          <t>Security and compliance readiness</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Can they pay you and sign with you without an internal argument</t>
+          <t>Can they assess your risk without a six week detour</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Has to be built, and it is the expensive one</t>
         </is>
       </c>
     </row>
@@ -936,12 +988,17 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Follow-through</t>
+          <t>Champion enablement</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Does the process after the call look like it will hold</t>
+          <t>Can your advocate carry you through four departments that never met you</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Free, and almost nobody does it</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1093,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>(a) Nothing findable (b) A code profile (c) A portfolio of work (d) Work plus written explanation of how I approach it (e) That, plus something a past client said, published</t>
+          <t>(a) Nothing findable (b) A code profile (c) A portfolio of work (d) Work plus a written explanation of how you approach it (e) That, plus a named client, their job title, and what you actually did</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1046,7 +1103,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Proof. Separates people with no artifacts from people with the wrong artifacts. A code profile proves you can build, which was never in doubt</t>
+          <t>Proof. Option (e) is the research's own standard: attributable, specific, verifiable. A code profile proves you can build, which was never in doubt</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1118,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>(a) We agree as we go (b) A verbal or chat outline (c) A written list of tasks (d) A written scope with what is excluded (e) That, plus stated milestones and an end point</t>
+          <t>(a) We agree as we go (b) A verbal or chat outline (c) A written list of tasks (d) A written scope with what is excluded (e) That, plus milestones, an end point, and what happens if it changes</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -1071,7 +1128,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Scope. Undefined scope is the most common reason a target market buyer stops replying after the first call</t>
+          <t>Scope. Undefined scope is where a target market buyer stops replying after the first call</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1138,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>How do you arrive at your price?</t>
+          <t>Which of these do you already have ready to send?</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>(a) I ask what their budget is (b) My hourly rate times my estimate (c) What similar work goes for where I am (d) What the work is worth to their business (e) That, with options at different scopes</t>
+          <t>(a) None of them (b) An invoice (c) A completed W-8BEN or W-8BEN-E (d) That, plus a contract template you did not write from scratch (e) That, plus insurance certificates</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -1096,7 +1153,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Pricing frame. Option (c) is the thesis in miniature. It is the most common answer and it is anchored to the wrong reference</t>
+          <t>Paperwork readiness. Replaces the old vaguer question. A missing or invalid W-8 form means 30 percent withholding or no payment at all, and most respondents will not know what it is</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1163,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>If a buyer said yes today, what would happen next?</t>
+          <t>If a buyer asked how you handle their data and access, what could you send today?</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>(a) I would work out how to invoice them (b) I would send an invoice and hope it clears (c) I have a payment method that works (d) I have payment and a contract I can send (e) That, and I have done it with a buyer in that country before</t>
+          <t>(a) I would answer in an email (b) A written explanation of my setup (c) That, plus a recent security test (d) That, plus a page they can read without asking (e) A formal report, SOC 2 or equivalent</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1121,7 +1178,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Contracting and payment. Frequently the actual blocker and almost never the one people name. Also the field that tells you which market they are in</t>
+          <t>Security and compliance readiness. The dominant gate above band 2, and the most expensive to close. Option (a) is not a failure at band 1 and is fatal at band 3</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1188,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>In your last target market conversation that did not convert, do you know why?</t>
+          <t>After a good call, what does the person you spoke to have in hand to show their colleagues?</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>(a) No, they went quiet (b) They said budget (c) They said timing (d) They gave a specific reason about my proposal (e) I asked, and I changed something because of the answer</t>
+          <t>(a) Nothing, they have my email (b) A proposal (c) A proposal plus references (d) That, plus answers to the questions their legal and security people will ask (e) I ask who else has to approve it and give them something for each</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1146,7 +1203,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Diagnosis. Option (a) is the emotional core of the whole funnel, and it is the most selected answer in this audience</t>
+          <t>Champion enablement. The single most actionable question here, and the one nobody expects. It is free to fix and almost nobody does it</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1228,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Follow-through, and the segmentation signal. This single answer sorts Level 1 from Level 2 and decides which path the respondent is sent down</t>
+          <t>The segmentation signal. Sorts Level 1 from Level 2 and decides which path the respondent is sent down</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1247,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
   </cols>
@@ -1210,7 +1267,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Tier name</t>
+          <t>Band</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -1232,12 +1289,12 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not yet visible</t>
+          <t>Band 1. Direct work only</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>You can build. That is not what this measures. What it shows is that a buyer in the United States or Canada currently has almost nothing to go on, and the checks they run happen after your conversation ends, where you cannot see them. Your weakest dimension is {dimension}. Nothing here is about your ability</t>
+          <t>You can build. That is not what this measures. What it shows is that your setup currently works only where one person decides and no formal process runs. That is most marketplace and referral work, and it is a real place to be. Your weakest dimension is {dimension}. Nothing here is about your ability</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -1254,12 +1311,12 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Legible, not yet convincing</t>
+          <t>Band 2. Clears a light review</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>A buyer can tell what you do. They cannot yet verify it or work out what they are buying. Your weakest dimension is {dimension}, and it is the one that decides whether the second conversation happens</t>
+          <t>You would survive a buyer who does a little checking and stall at one who does it properly. Your weakest dimension is {dimension}, and it is the one that decides whether the second conversation happens. Some of what is missing is free to fix. Some of it is not, and we will tell you which</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1276,12 +1333,12 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Ready, and losing on something specific</t>
+          <t>Band 3. Clears procurement, mostly</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>You clear most of what a buyer checks. At this level the losses are narrow and specific, usually one dimension applied to one deal. Yours is {dimension}</t>
+          <t>You clear most of what a buyer verifies. At this level the losses are narrow and specific, usually one dimension applied to one deal. Yours is {dimension}</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -1448,12 +1505,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="61" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1479,6 +1537,11 @@
           <t>Routes toward</t>
         </is>
       </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Free or costs money</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1496,6 +1559,11 @@
           <t>Positioning review</t>
         </is>
       </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1505,12 +1573,17 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>What a buyer can verify without asking</t>
+          <t>What counts as verifiable, and what gets discounted</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>The proof gap, hardest to fix, longest nurture</t>
+          <t>The proof gap. Longest nurture, because it needs a client to exist first</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Free, slow</t>
         </is>
       </c>
     </row>
@@ -1530,55 +1603,75 @@
           <t>Teardown, scope half</t>
         </is>
       </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Pricing frame</t>
+          <t>Paperwork readiness</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>What the price is attached to</t>
+          <t>The form that withholds 30 percent of your invoice</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Teardown, pricing half</t>
+          <t>The build list. Strongest single email in the sequence</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Mixed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Contracting and payment</t>
+          <t>Security and compliance readiness</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>The deal that dies at the paperwork</t>
+          <t>What to send when you do not have SOC 2</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Route by market. This respondent has a rail problem, and so does the checkout they are about to meet</t>
+          <t>The build list, expensive half</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Costs money</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Follow-through</t>
+          <t>Champion enablement</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>What happens after they say yes</t>
+          <t>The three people your champion has to convince without you</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Room, mechanics and accountability</t>
+          <t>Teardown, champion half</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Free</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1792,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Starts, completions, completion rate by question, drop-off question, and question 7 distribution. Question 7 distribution is the most useful number this business will have in month one</t>
+          <t>Starts, completions, completion rate by question, drop-off question, question 7 distribution, and band distribution. Question 7 distribution and band distribution together are the most useful numbers this business will have in month one: they say whether the audience being reached is at a band the offer can serve</t>
         </is>
       </c>
     </row>
